--- a/data/trans_dic/P19C05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,0</t>
+          <t>11,92; 18,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 20,38</t>
+          <t>14,02; 20,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 13,29</t>
+          <t>7,73; 12,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,99</t>
+          <t>8,27; 12,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 21,16</t>
+          <t>15,06; 20,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 23,15</t>
+          <t>16,65; 23,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,68</t>
+          <t>9,21; 14,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 15,9</t>
+          <t>12,28; 16,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 18,8</t>
+          <t>14,06; 18,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,4; 21,0</t>
+          <t>16,08; 20,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 13,36</t>
+          <t>9,25; 13,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 13,72</t>
+          <t>10,87; 13,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 16,22</t>
+          <t>11,36; 16,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,54</t>
+          <t>11,65; 16,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,24</t>
+          <t>9,55; 14,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,4</t>
+          <t>3,93; 10,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,1; 18,06</t>
+          <t>12,75; 18,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 21,12</t>
+          <t>16,04; 21,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,24</t>
+          <t>9,67; 14,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 10,67</t>
+          <t>7,74; 10,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 16,5</t>
+          <t>12,79; 16,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,28</t>
+          <t>14,61; 18,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 13,61</t>
+          <t>10,26; 13,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,73</t>
+          <t>5,38; 9,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,11; 18,4</t>
+          <t>11,69; 18,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 16,44</t>
+          <t>10,33; 16,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,88</t>
+          <t>5,92; 10,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 11,93</t>
+          <t>7,73; 12,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 20,02</t>
+          <t>14,14; 19,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,83</t>
+          <t>14,22; 20,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,28</t>
+          <t>7,91; 13,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,53</t>
+          <t>4,36; 12,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 18,02</t>
+          <t>13,3; 18,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 17,63</t>
+          <t>13,31; 17,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,13</t>
+          <t>7,66; 11,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,46</t>
+          <t>6,11; 11,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,5</t>
+          <t>9,55; 14,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,42; 18,94</t>
+          <t>13,5; 18,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 14,14</t>
+          <t>9,39; 14,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,71</t>
+          <t>9,58; 13,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 18,15</t>
+          <t>12,94; 18,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,3</t>
+          <t>14,98; 20,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,6</t>
+          <t>9,93; 14,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,69</t>
+          <t>10,05; 14,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 15,8</t>
+          <t>12,06; 15,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 18,66</t>
+          <t>15,01; 18,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 13,55</t>
+          <t>10,08; 13,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 13,67</t>
+          <t>10,58; 13,62</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 14,88</t>
+          <t>12,36; 15,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 16,52</t>
+          <t>13,72; 16,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,43; 11,87</t>
+          <t>9,51; 11,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,78</t>
+          <t>7,38; 10,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,76; 17,67</t>
+          <t>14,82; 17,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 19,64</t>
+          <t>16,83; 19,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,95</t>
+          <t>10,34; 12,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,23</t>
+          <t>9,11; 12,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 16,0</t>
+          <t>13,99; 15,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 17,75</t>
+          <t>15,71; 17,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,11</t>
+          <t>10,31; 12,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 11,33</t>
+          <t>8,98; 11,25</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56892; 86034</t>
+          <t>56951; 89089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83699; 123520</t>
+          <t>84980; 123355</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41054; 69749</t>
+          <t>40608; 68109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51884; 79425</t>
+          <t>50535; 78443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>80338; 113871</t>
+          <t>81012; 112321</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106763; 147200</t>
+          <t>105881; 147427</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50543; 79934</t>
+          <t>50140; 80802</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79728; 103600</t>
+          <t>80038; 104348</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>142681; 190964</t>
+          <t>142886; 191770</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203617; 260769</t>
+          <t>199716; 258617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101856; 142880</t>
+          <t>98937; 141053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>138672; 173243</t>
+          <t>137245; 174861</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79041; 117133</t>
+          <t>82002; 119209</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101124; 143391</t>
+          <t>100987; 143559</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78578; 116262</t>
+          <t>77934; 115321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46521; 121325</t>
+          <t>45868; 118979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>105347; 145229</t>
+          <t>102531; 145660</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>143354; 189839</t>
+          <t>144131; 191932</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83196; 123341</t>
+          <t>83784; 124909</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73243; 100499</t>
+          <t>72956; 98965</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>193600; 251777</t>
+          <t>195292; 250583</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257422; 322786</t>
+          <t>257999; 321900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172686; 229091</t>
+          <t>172676; 228870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>111851; 205212</t>
+          <t>113408; 203361</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65984; 100319</t>
+          <t>63730; 98233</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67996; 104572</t>
+          <t>65730; 104996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32846; 59869</t>
+          <t>32577; 59321</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52133; 81904</t>
+          <t>53069; 84099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81381; 117026</t>
+          <t>82675; 116386</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98709; 141303</t>
+          <t>96490; 138918</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45575; 77000</t>
+          <t>45871; 77873</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34517; 115531</t>
+          <t>40188; 117421</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>155545; 203624</t>
+          <t>150213; 203298</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>176191; 231711</t>
+          <t>174943; 229891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85482; 125733</t>
+          <t>86613; 127802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89059; 184261</t>
+          <t>98261; 182612</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68215; 102916</t>
+          <t>67769; 101612</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108106; 152633</t>
+          <t>108732; 150409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73295; 109221</t>
+          <t>72536; 110230</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86734; 122055</t>
+          <t>85219; 119033</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106721; 147743</t>
+          <t>105351; 149056</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>140138; 189461</t>
+          <t>139778; 187086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85256; 128000</t>
+          <t>87071; 127375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>108914; 156128</t>
+          <t>106798; 156545</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>186346; 240799</t>
+          <t>183718; 234995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>262259; 324494</t>
+          <t>261034; 323686</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>169054; 223560</t>
+          <t>166238; 220702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210268; 267011</t>
+          <t>206552; 266043</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>301710; 365333</t>
+          <t>303299; 369199</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>397309; 481554</t>
+          <t>400015; 479745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>251292; 316354</t>
+          <t>253386; 318699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>244798; 361711</t>
+          <t>247443; 360860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>404636; 484194</t>
+          <t>406123; 483010</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>528109; 617858</t>
+          <t>529515; 620549</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>299632; 371248</t>
+          <t>296557; 369711</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>312993; 437865</t>
+          <t>326155; 438160</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>729461; 831117</t>
+          <t>726894; 827500</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>950909; 1076018</t>
+          <t>952121; 1068420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>571410; 669867</t>
+          <t>570141; 667864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>620979; 785501</t>
+          <t>622322; 779952</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 18,64</t>
+          <t>12,07; 18,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,02; 20,36</t>
+          <t>14,17; 20,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,97</t>
+          <t>7,89; 13,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 12,83</t>
+          <t>8,03; 12,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,06; 20,87</t>
+          <t>14,54; 21,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 23,19</t>
+          <t>16,88; 23,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,84</t>
+          <t>9,37; 15,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 16,02</t>
+          <t>11,72; 15,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 18,88</t>
+          <t>13,89; 18,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 20,83</t>
+          <t>16,38; 20,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,19</t>
+          <t>9,42; 13,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 13,85</t>
+          <t>10,62; 13,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 16,51</t>
+          <t>11,15; 16,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,56</t>
+          <t>11,58; 16,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,13</t>
+          <t>9,52; 14,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,2</t>
+          <t>7,66; 11,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,75; 18,11</t>
+          <t>12,58; 17,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,04; 21,35</t>
+          <t>16,16; 21,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 14,42</t>
+          <t>9,85; 14,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,5</t>
+          <t>7,82; 10,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 16,42</t>
+          <t>12,71; 16,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,23</t>
+          <t>14,6; 18,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 13,6</t>
+          <t>10,27; 13,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,64</t>
+          <t>8,02; 10,31</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 18,02</t>
+          <t>11,87; 18,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,51</t>
+          <t>10,44; 16,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,78</t>
+          <t>5,92; 10,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,25</t>
+          <t>8,3; 12,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 19,91</t>
+          <t>13,71; 19,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,22; 20,47</t>
+          <t>14,53; 20,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 13,43</t>
+          <t>7,91; 13,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,73</t>
+          <t>10,56; 14,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 18,0</t>
+          <t>13,6; 17,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,49</t>
+          <t>13,39; 17,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,31</t>
+          <t>7,54; 11,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,35</t>
+          <t>9,91; 12,96</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,32</t>
+          <t>9,71; 14,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,67</t>
+          <t>13,53; 18,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,27</t>
+          <t>9,51; 13,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,38</t>
+          <t>9,84; 13,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 18,31</t>
+          <t>12,89; 18,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 20,05</t>
+          <t>15,29; 20,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,53</t>
+          <t>9,85; 14,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 14,73</t>
+          <t>12,01; 15,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 15,42</t>
+          <t>12,03; 15,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 18,61</t>
+          <t>15,05; 18,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 13,38</t>
+          <t>10,12; 13,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 13,62</t>
+          <t>11,59; 14,12</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,04</t>
+          <t>12,22; 15,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,72; 16,46</t>
+          <t>13,75; 16,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 11,96</t>
+          <t>9,57; 11,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,76</t>
+          <t>9,37; 11,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 17,62</t>
+          <t>14,73; 17,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 19,72</t>
+          <t>16,74; 19,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,89</t>
+          <t>10,39; 12,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,24</t>
+          <t>11,31; 13,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,99; 15,93</t>
+          <t>13,91; 15,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 17,63</t>
+          <t>15,67; 17,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 12,07</t>
+          <t>10,38; 12,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,25</t>
+          <t>10,62; 12,01</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>66989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91566</t>
+          <t>96796</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>163785</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56951; 89089</t>
+          <t>57690; 87535</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84980; 123355</t>
+          <t>85870; 123999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40608; 68109</t>
+          <t>41411; 69920</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50535; 78443</t>
+          <t>52948; 80563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81012; 112321</t>
+          <t>78250; 113193</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>105881; 147427</t>
+          <t>107319; 147781</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50140; 80802</t>
+          <t>51025; 82098</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80038; 104348</t>
+          <t>82771; 109879</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>142886; 191770</t>
+          <t>141079; 190049</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>199716; 258617</t>
+          <t>203391; 257959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98937; 141053</t>
+          <t>100716; 140549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>137245; 174861</t>
+          <t>145075; 182385</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87703</t>
+          <t>94257</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>85985</t>
+          <t>95204</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>173688</t>
+          <t>189461</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82002; 119209</t>
+          <t>80500; 118438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100987; 143559</t>
+          <t>100431; 143578</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77934; 115321</t>
+          <t>77745; 116322</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45868; 118979</t>
+          <t>77879; 115146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>102531; 145660</t>
+          <t>101145; 142931</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>144131; 191932</t>
+          <t>145232; 192045</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83784; 124909</t>
+          <t>85363; 127957</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72956; 98965</t>
+          <t>81977; 111503</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195292; 250583</t>
+          <t>194027; 249541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257999; 321900</t>
+          <t>257786; 327258</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172676; 228870</t>
+          <t>172821; 227431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>113408; 203361</t>
+          <t>165429; 212827</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84498</t>
+          <t>98171</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>151161</t>
+          <t>178820</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63730; 98233</t>
+          <t>64722; 98844</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65730; 104996</t>
+          <t>66421; 105444</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32577; 59321</t>
+          <t>32583; 59542</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53069; 84099</t>
+          <t>64226; 98920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82675; 116386</t>
+          <t>80176; 116512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96490; 138918</t>
+          <t>98602; 141568</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45871; 77873</t>
+          <t>45864; 77392</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40188; 117421</t>
+          <t>83991; 116236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150213; 203298</t>
+          <t>153690; 201496</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174943; 229891</t>
+          <t>175993; 232930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86613; 127802</t>
+          <t>85205; 127347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98261; 182612</t>
+          <t>155510; 203407</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102583</t>
+          <t>110445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>135881</t>
+          <t>147361</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>238464</t>
+          <t>257806</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67769; 101612</t>
+          <t>68942; 101889</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108732; 150409</t>
+          <t>108984; 151153</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72536; 110230</t>
+          <t>73488; 106617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85219; 119033</t>
+          <t>93263; 130600</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105351; 149056</t>
+          <t>104887; 147262</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>139778; 187086</t>
+          <t>142655; 188026</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87071; 127375</t>
+          <t>86337; 126657</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>106798; 156545</t>
+          <t>129286; 166370</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183718; 234995</t>
+          <t>183300; 236114</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>261034; 323686</t>
+          <t>261746; 329150</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166238; 220702</t>
+          <t>166850; 220369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>206552; 266043</t>
+          <t>234644; 285821</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320615</t>
+          <t>352339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>437533</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>718545</t>
+          <t>789872</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>303299; 369199</t>
+          <t>299928; 369344</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>400015; 479745</t>
+          <t>400853; 482157</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253386; 318699</t>
+          <t>254844; 317446</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>247443; 360860</t>
+          <t>318270; 390567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>406123; 483010</t>
+          <t>403825; 477766</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>529515; 620549</t>
+          <t>526808; 614330</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>296557; 369711</t>
+          <t>298011; 372425</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>326155; 438160</t>
+          <t>410127; 473377</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>726894; 827500</t>
+          <t>722756; 825630</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>952121; 1068420</t>
+          <t>949783; 1070834</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>570141; 667864</t>
+          <t>574241; 672027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>622322; 779952</t>
+          <t>746058; 843528</t>
         </is>
       </c>
     </row>
